--- a/sponsorship_application_forms/031_sponsorship_review_panel_registration--sponsorship_application_forms.xlsx
+++ b/sponsorship_application_forms/031_sponsorship_review_panel_registration--sponsorship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>apply_note</t>
+          <t>apply_note_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Apply Note</t>
+          <t>Apply Note 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>panelist_availability</t>
+          <t>panelist_availability_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Panelist Availability</t>
+          <t>Panelist Availability 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>review_period</t>
+          <t>review_period_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Review Period</t>
+          <t>Review Period 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>apply_frequency</t>
+          <t>apply_frequency_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Apply Frequency</t>
+          <t>Apply Frequency 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>review_frequency</t>
+          <t>review_frequency_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Review Frequency</t>
+          <t>Review Frequency 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>confirm_review</t>
+          <t>confirm_review_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Confirm Review</t>
+          <t>Confirm Review 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>panelist_availability_choices</t>
+          <t>panelist_availability_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>panelist_availability_choices</t>
+          <t>panelist_availability_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>panelist_availability_choices</t>
+          <t>panelist_availability_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>panelist_availability_choices</t>
+          <t>panelist_availability_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>panelist_availability_choices</t>
+          <t>panelist_availability_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>review_period_choices</t>
+          <t>review_period_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>apply_frequency_choices</t>
+          <t>apply_frequency_2_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>review_frequency_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>confirm_review_choices</t>
+          <t>confirm_review_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>confirm_review_choices</t>
+          <t>confirm_review_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
